--- a/reports/Debug-snowbowl-20260106/snowbowl_Report_20260106.xlsx
+++ b/reports/Debug-snowbowl-20260106/snowbowl_Report_20260106.xlsx
@@ -1084,7 +1084,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="4">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C6" s="4">
         <v>150</v>
@@ -1093,7 +1093,7 @@
         <v>161</v>
       </c>
       <c r="E6" s="4">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="F6" s="4">
         <v>1575</v>
@@ -1105,7 +1105,7 @@
         <v>1229</v>
       </c>
       <c r="I6" s="4">
-        <v>2680</v>
+        <v>2282</v>
       </c>
       <c r="J6" s="4">
         <v>1850</v>
@@ -1114,7 +1114,7 @@
         <v>2232</v>
       </c>
       <c r="L6" s="4">
-        <v>11726</v>
+        <v>10541</v>
       </c>
       <c r="M6" s="4">
         <v>8450</v>
@@ -1202,7 +1202,7 @@
         <v>8149</v>
       </c>
       <c r="L8" s="4">
-        <v>62589</v>
+        <v>62585</v>
       </c>
       <c r="M8" s="4">
         <v>53900</v>
@@ -1246,7 +1246,7 @@
         <v>1047</v>
       </c>
       <c r="L9" s="4">
-        <v>11897</v>
+        <v>11893</v>
       </c>
       <c r="M9" s="4">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="4">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="C10" s="4">
         <v>2250</v>
@@ -1269,7 +1269,7 @@
         <v>2585</v>
       </c>
       <c r="E10" s="4">
-        <v>5774</v>
+        <v>5761</v>
       </c>
       <c r="F10" s="4">
         <v>19625</v>
@@ -1281,7 +1281,7 @@
         <v>17061</v>
       </c>
       <c r="I10" s="4">
-        <v>19144</v>
+        <v>18746</v>
       </c>
       <c r="J10" s="4">
         <v>17300</v>
@@ -1290,7 +1290,7 @@
         <v>18053</v>
       </c>
       <c r="L10" s="4">
-        <v>128395</v>
+        <v>127202</v>
       </c>
       <c r="M10" s="4">
         <v>95825</v>
@@ -1353,7 +1353,7 @@
         <v>24</v>
       </c>
       <c r="B14" s="4">
-        <v>0</v>
+        <v>927.9400000000001</v>
       </c>
       <c r="C14" s="4">
         <v>911.72</v>
@@ -1362,7 +1362,7 @@
         <v>897.27</v>
       </c>
       <c r="E14" s="4">
-        <v>0</v>
+        <v>1855.88</v>
       </c>
       <c r="F14" s="4">
         <v>6382.04</v>
@@ -1374,7 +1374,7 @@
         <v>6280.89</v>
       </c>
       <c r="I14" s="4">
-        <v>0</v>
+        <v>5567.64</v>
       </c>
       <c r="J14" s="4">
         <v>5470.32</v>
@@ -1383,7 +1383,7 @@
         <v>5383.62</v>
       </c>
       <c r="L14" s="4">
-        <v>0</v>
+        <v>62171.98</v>
       </c>
       <c r="M14" s="4">
         <v>61085.24</v>
@@ -1485,7 +1485,7 @@
         <v>27</v>
       </c>
       <c r="B17" s="4">
-        <v>0</v>
+        <v>5126.947819444444</v>
       </c>
       <c r="C17" s="4">
         <v>5715.51</v>
@@ -1494,7 +1494,7 @@
         <v>5951.56</v>
       </c>
       <c r="E17" s="4">
-        <v>0</v>
+        <v>10660.05366666666</v>
       </c>
       <c r="F17" s="4">
         <v>41053.61</v>
@@ -1506,7 +1506,7 @@
         <v>39842.53</v>
       </c>
       <c r="I17" s="4">
-        <v>0</v>
+        <v>32995.88015277777</v>
       </c>
       <c r="J17" s="4">
         <v>34816.66</v>
@@ -1515,7 +1515,7 @@
         <v>36722.38</v>
       </c>
       <c r="L17" s="4">
-        <v>850.3859722222222</v>
+        <v>261962.7616944442</v>
       </c>
       <c r="M17" s="4">
         <v>206596.14</v>
@@ -1617,7 +1617,7 @@
         <v>30</v>
       </c>
       <c r="B20" s="4">
-        <v>0</v>
+        <v>965.1112777777778</v>
       </c>
       <c r="C20" s="4">
         <v>1191.77</v>
@@ -1626,7 +1626,7 @@
         <v>1155.03</v>
       </c>
       <c r="E20" s="4">
-        <v>0</v>
+        <v>2253.628666666667</v>
       </c>
       <c r="F20" s="4">
         <v>9208.799999999999</v>
@@ -1638,7 +1638,7 @@
         <v>8792.200000000001</v>
       </c>
       <c r="I20" s="4">
-        <v>1459.958177777778</v>
+        <v>7054.486372222223</v>
       </c>
       <c r="J20" s="4">
         <v>7906.53</v>
@@ -1647,7 +1647,7 @@
         <v>7637.21</v>
       </c>
       <c r="L20" s="4">
-        <v>17894.51824444445</v>
+        <v>82245.77263333331</v>
       </c>
       <c r="M20" s="4">
         <v>81246.5</v>
@@ -1749,7 +1749,7 @@
         <v>33</v>
       </c>
       <c r="B23" s="4">
-        <v>147.358625</v>
+        <v>2625.709569444445</v>
       </c>
       <c r="C23" s="4">
         <v>2725.11</v>
@@ -1758,7 +1758,7 @@
         <v>1458.23</v>
       </c>
       <c r="E23" s="4">
-        <v>338.1983333333333</v>
+        <v>4976.491527777777</v>
       </c>
       <c r="F23" s="4">
         <v>15890.79</v>
@@ -1770,7 +1770,7 @@
         <v>14825.91</v>
       </c>
       <c r="I23" s="4">
-        <v>338.1983333333333</v>
+        <v>11111.58988888889</v>
       </c>
       <c r="J23" s="4">
         <v>13165.68</v>
@@ -1779,7 +1779,7 @@
         <v>13729.85</v>
       </c>
       <c r="L23" s="4">
-        <v>1030.145791666667</v>
+        <v>169543.5870416666</v>
       </c>
       <c r="M23" s="4">
         <v>162031.8</v>
@@ -1881,7 +1881,7 @@
         <v>36</v>
       </c>
       <c r="B26" s="4">
-        <v>0</v>
+        <v>631.0268194444445</v>
       </c>
       <c r="C26" s="4">
         <v>903.9299999999999</v>
@@ -1890,7 +1890,7 @@
         <v>792.37</v>
       </c>
       <c r="E26" s="4">
-        <v>177.0521666666667</v>
+        <v>1334.847541666667</v>
       </c>
       <c r="F26" s="4">
         <v>6657.1</v>
@@ -1902,7 +1902,7 @@
         <v>4284.83</v>
       </c>
       <c r="I26" s="4">
-        <v>268.0157083333334</v>
+        <v>4425.594277777777</v>
       </c>
       <c r="J26" s="4">
         <v>4723.57</v>
@@ -1911,7 +1911,7 @@
         <v>3717.27</v>
       </c>
       <c r="L26" s="4">
-        <v>7305.990597222221</v>
+        <v>45617.34373611112</v>
       </c>
       <c r="M26" s="4">
         <v>31987.61</v>
@@ -2013,7 +2013,7 @@
         <v>39</v>
       </c>
       <c r="B29" s="4">
-        <v>0</v>
+        <v>1222.140291666667</v>
       </c>
       <c r="C29" s="4">
         <v>1436.29</v>
@@ -2022,7 +2022,7 @@
         <v>712.01</v>
       </c>
       <c r="E29" s="4">
-        <v>85.09916666666666</v>
+        <v>1654.700625</v>
       </c>
       <c r="F29" s="4">
         <v>9718.700000000001</v>
@@ -2034,7 +2034,7 @@
         <v>5790.46</v>
       </c>
       <c r="I29" s="4">
-        <v>210.0869444444444</v>
+        <v>4137.869111111111</v>
       </c>
       <c r="J29" s="4">
         <v>8463.690000000001</v>
@@ -2043,7 +2043,7 @@
         <v>5560.06</v>
       </c>
       <c r="L29" s="4">
-        <v>425.1494444444444</v>
+        <v>44210.24177777777</v>
       </c>
       <c r="M29" s="4">
         <v>66678.52</v>
@@ -2145,7 +2145,7 @@
         <v>42</v>
       </c>
       <c r="B32" s="4">
-        <v>0</v>
+        <v>1178.540833333333</v>
       </c>
       <c r="C32" s="4">
         <v>1140</v>
@@ -2154,7 +2154,7 @@
         <v>803.36</v>
       </c>
       <c r="E32" s="4">
-        <v>0</v>
+        <v>1846.104444444444</v>
       </c>
       <c r="F32" s="4">
         <v>4560</v>
@@ -2166,7 +2166,7 @@
         <v>4504.83</v>
       </c>
       <c r="I32" s="4">
-        <v>0</v>
+        <v>3324.706944444445</v>
       </c>
       <c r="J32" s="4">
         <v>3825</v>
@@ -2175,7 +2175,7 @@
         <v>3505.94</v>
       </c>
       <c r="L32" s="4">
-        <v>0</v>
+        <v>46541.74180555559</v>
       </c>
       <c r="M32" s="4">
         <v>43750</v>
@@ -2277,7 +2277,7 @@
         <v>45</v>
       </c>
       <c r="B35" s="4">
-        <v>0</v>
+        <v>3775.860319444445</v>
       </c>
       <c r="C35" s="4">
         <v>2875.17</v>
@@ -2286,7 +2286,7 @@
         <v>2958.41</v>
       </c>
       <c r="E35" s="4">
-        <v>0</v>
+        <v>7400.847972222223</v>
       </c>
       <c r="F35" s="4">
         <v>23138.99</v>
@@ -2298,7 +2298,7 @@
         <v>21386.46</v>
       </c>
       <c r="I35" s="4">
-        <v>803.0555555555555</v>
+        <v>22172.43877777777</v>
       </c>
       <c r="J35" s="4">
         <v>19136.32</v>
@@ -2307,7 +2307,7 @@
         <v>18311.98</v>
       </c>
       <c r="L35" s="4">
-        <v>5843.437499999999</v>
+        <v>195916.8360277777</v>
       </c>
       <c r="M35" s="4">
         <v>143937.74</v>
@@ -2409,7 +2409,7 @@
         <v>48</v>
       </c>
       <c r="B38" s="4">
-        <v>105.46875</v>
+        <v>2305.968652777778</v>
       </c>
       <c r="C38" s="4">
         <v>2203.18</v>
@@ -2418,7 +2418,7 @@
         <v>2397.92</v>
       </c>
       <c r="E38" s="4">
-        <v>368.3355694444444</v>
+        <v>4896.423222222223</v>
       </c>
       <c r="F38" s="4">
         <v>16087.97</v>
@@ -2430,7 +2430,7 @@
         <v>14744.23</v>
       </c>
       <c r="I38" s="4">
-        <v>868.1789027777778</v>
+        <v>16161.02240277778</v>
       </c>
       <c r="J38" s="4">
         <v>15424.71</v>
@@ -2439,7 +2439,7 @@
         <v>13994.21</v>
       </c>
       <c r="L38" s="4">
-        <v>3624.134236111111</v>
+        <v>122332.8621666667</v>
       </c>
       <c r="M38" s="4">
         <v>104244.79</v>
@@ -2453,7 +2453,7 @@
         <v>49</v>
       </c>
       <c r="B39" s="5">
-        <v>0.1058564598699196</v>
+        <v>2.314445541016304</v>
       </c>
       <c r="C39" s="5">
         <v>2.022379291353038</v>
@@ -2462,7 +2462,7 @@
         <v>2.211735650586498</v>
       </c>
       <c r="E39" s="5">
-        <v>0.1569018783828597</v>
+        <v>2.085755665907787</v>
       </c>
       <c r="F39" s="5">
         <v>1.293100690517699</v>
@@ -2474,7 +2474,7 @@
         <v>4.805213144738395</v>
       </c>
       <c r="I39" s="5">
-        <v>0.08021733371631784</v>
+        <v>1.493233852069709</v>
       </c>
       <c r="J39" s="5">
         <v>1.358770644012135</v>
@@ -2483,7 +2483,7 @@
         <v>3.261222343442295</v>
       </c>
       <c r="L39" s="5">
-        <v>0.06814293486283469</v>
+        <v>2.300168734133977</v>
       </c>
       <c r="M39" s="5">
         <v>1.833368302441219</v>
@@ -2541,7 +2541,7 @@
         <v>51</v>
       </c>
       <c r="B41" s="4">
-        <v>0</v>
+        <v>1017.069722222222</v>
       </c>
       <c r="C41" s="4">
         <v>3577.79</v>
@@ -2550,7 +2550,7 @@
         <v>2928.06</v>
       </c>
       <c r="E41" s="4">
-        <v>0</v>
+        <v>2345.677958333334</v>
       </c>
       <c r="F41" s="4">
         <v>47865.55</v>
@@ -2562,7 +2562,7 @@
         <v>32544.25</v>
       </c>
       <c r="I41" s="4">
-        <v>248</v>
+        <v>14710.33429166667</v>
       </c>
       <c r="J41" s="4">
         <v>31183.69</v>
@@ -2571,7 +2571,7 @@
         <v>100905.26</v>
       </c>
       <c r="L41" s="4">
-        <v>4784.319999999998</v>
+        <v>239640.931125</v>
       </c>
       <c r="M41" s="4">
         <v>241533</v>
@@ -2585,7 +2585,7 @@
         <v>52</v>
       </c>
       <c r="B42" s="5">
-        <v>0</v>
+        <v>17.51156118075655</v>
       </c>
       <c r="C42" s="5">
         <v>35.77074585082983</v>
@@ -2594,7 +2594,7 @@
         <v>73.82402105756795</v>
       </c>
       <c r="E42" s="5">
-        <v>0</v>
+        <v>16.6655982807305</v>
       </c>
       <c r="F42" s="5">
         <v>35.25461991146857</v>
@@ -2606,7 +2606,7 @@
         <v>66.50167387007384</v>
       </c>
       <c r="I42" s="5">
-        <v>0.3122404422634058</v>
+        <v>18.52081163335704</v>
       </c>
       <c r="J42" s="5">
         <v>24.92760817605538</v>
@@ -2615,7 +2615,7 @@
         <v>74.05728667365659</v>
       </c>
       <c r="L42" s="5">
-        <v>0.9451392265473427</v>
+        <v>47.34090618783185</v>
       </c>
       <c r="M42" s="5">
         <v>31.40618051600521</v>
@@ -2673,7 +2673,7 @@
         <v>54</v>
       </c>
       <c r="B44" s="4">
-        <v>0</v>
+        <v>2709.624111111111</v>
       </c>
       <c r="C44" s="4">
         <v>2211.5</v>
@@ -2682,7 +2682,7 @@
         <v>2825.94</v>
       </c>
       <c r="E44" s="4">
-        <v>0</v>
+        <v>5237.825083333334</v>
       </c>
       <c r="F44" s="4">
         <v>17334.32</v>
@@ -2694,7 +2694,7 @@
         <v>17650.8</v>
       </c>
       <c r="I44" s="4">
-        <v>302.9244166666667</v>
+        <v>15901.07436111111</v>
       </c>
       <c r="J44" s="4">
         <v>16514.16</v>
@@ -2703,7 +2703,7 @@
         <v>17740.83</v>
       </c>
       <c r="L44" s="4">
-        <v>2064.372333333334</v>
+        <v>99009.13138888881</v>
       </c>
       <c r="M44" s="4">
         <v>105460.8</v>
@@ -2717,7 +2717,7 @@
         <v>55</v>
       </c>
       <c r="B45" s="5">
-        <v>0</v>
+        <v>8.11704579760622</v>
       </c>
       <c r="C45" s="5">
         <v>9.398240618758233</v>
@@ -2726,7 +2726,7 @@
         <v>7.956868688887994</v>
       </c>
       <c r="E45" s="5">
-        <v>0</v>
+        <v>7.329149529065196</v>
       </c>
       <c r="F45" s="5">
         <v>7.073038567628001</v>
@@ -2738,7 +2738,7 @@
         <v>13.97474256959403</v>
       </c>
       <c r="I45" s="5">
-        <v>0.1032531024704157</v>
+        <v>5.419950225419283</v>
       </c>
       <c r="J45" s="5">
         <v>6.39877868747651</v>
@@ -2747,7 +2747,7 @@
         <v>7.288232023773808</v>
       </c>
       <c r="L45" s="5">
-        <v>0.1371878405375149</v>
+        <v>6.579650729383962</v>
       </c>
       <c r="M45" s="5">
         <v>7.1811556356936</v>
@@ -2805,7 +2805,7 @@
         <v>57</v>
       </c>
       <c r="B47" s="4">
-        <v>0</v>
+        <v>163.1788888888889</v>
       </c>
       <c r="C47" s="4">
         <v>324</v>
@@ -2814,7 +2814,7 @@
         <v>334.82</v>
       </c>
       <c r="E47" s="4">
-        <v>0</v>
+        <v>325.7927083333333</v>
       </c>
       <c r="F47" s="4">
         <v>2218</v>
@@ -2826,7 +2826,7 @@
         <v>2283.49</v>
       </c>
       <c r="I47" s="4">
-        <v>115.9381944444444</v>
+        <v>1448.253791666667</v>
       </c>
       <c r="J47" s="4">
         <v>1985</v>
@@ -2835,7 +2835,7 @@
         <v>1927.18</v>
       </c>
       <c r="L47" s="4">
-        <v>115.9381944444444</v>
+        <v>17357.91608333333</v>
       </c>
       <c r="M47" s="4">
         <v>21091.2</v>
@@ -2946,7 +2946,7 @@
         <v>172.33</v>
       </c>
       <c r="E50" s="4">
-        <v>0</v>
+        <v>165.9145833333334</v>
       </c>
       <c r="F50" s="4">
         <v>1275.12</v>
@@ -2958,7 +2958,7 @@
         <v>1138.72</v>
       </c>
       <c r="I50" s="4">
-        <v>0</v>
+        <v>559.7344861111112</v>
       </c>
       <c r="J50" s="4">
         <v>1092.96</v>
@@ -2967,7 +2967,7 @@
         <v>1053.96</v>
       </c>
       <c r="L50" s="4">
-        <v>0</v>
+        <v>4985.334694444447</v>
       </c>
       <c r="M50" s="4">
         <v>8561.52</v>
@@ -2990,7 +2990,7 @@
         <v>18.10189075630252</v>
       </c>
       <c r="E51" s="5">
-        <v>0</v>
+        <v>12.28696565530895</v>
       </c>
       <c r="F51" s="5">
         <v>17.03257657927217</v>
@@ -3002,7 +3002,7 @@
         <v>18.5750312378678</v>
       </c>
       <c r="I51" s="5">
-        <v>0</v>
+        <v>9.008186630516692</v>
       </c>
       <c r="J51" s="5">
         <v>16.4458260982091</v>
@@ -3011,7 +3011,7 @@
         <v>22.15770408881919</v>
       </c>
       <c r="L51" s="5">
-        <v>0</v>
+        <v>18.81428058773771</v>
       </c>
       <c r="M51" s="5">
         <v>19.15324145734764</v>
@@ -3069,7 +3069,7 @@
         <v>63</v>
       </c>
       <c r="B53" s="4">
-        <v>0</v>
+        <v>635.8535000000001</v>
       </c>
       <c r="C53" s="4">
         <v>468.05</v>
@@ -3078,7 +3078,7 @@
         <v>848.5700000000001</v>
       </c>
       <c r="E53" s="4">
-        <v>0</v>
+        <v>1136.806472222222</v>
       </c>
       <c r="F53" s="4">
         <v>3772.76</v>
@@ -3090,7 +3090,7 @@
         <v>4877.4</v>
       </c>
       <c r="I53" s="4">
-        <v>0</v>
+        <v>3728.117430555556</v>
       </c>
       <c r="J53" s="4">
         <v>3249.54</v>
@@ -3099,7 +3099,7 @@
         <v>3636.4</v>
       </c>
       <c r="L53" s="4">
-        <v>0</v>
+        <v>39454.13794444445</v>
       </c>
       <c r="M53" s="4">
         <v>33756.39</v>
@@ -3113,7 +3113,7 @@
         <v>64</v>
       </c>
       <c r="B54" s="5">
-        <v>0</v>
+        <v>7.317483954791467</v>
       </c>
       <c r="C54" s="5">
         <v>3.809403664124623</v>
@@ -3122,7 +3122,7 @@
         <v>4.588293436226631</v>
       </c>
       <c r="E54" s="5">
-        <v>0</v>
+        <v>5.827989530504093</v>
       </c>
       <c r="F54" s="5">
         <v>3.192440686043553</v>
@@ -3134,7 +3134,7 @@
         <v>6.166506289965374</v>
       </c>
       <c r="I54" s="5">
-        <v>0</v>
+        <v>4.082826004762516</v>
       </c>
       <c r="J54" s="5">
         <v>3.193037289342707</v>
@@ -3143,7 +3143,7 @@
         <v>4.763605238550986</v>
       </c>
       <c r="L54" s="5">
-        <v>0</v>
+        <v>6.534098595225791</v>
       </c>
       <c r="M54" s="5">
         <v>5.782423168070416</v>
@@ -3333,7 +3333,7 @@
         <v>69</v>
       </c>
       <c r="B59" s="4">
-        <v>0</v>
+        <v>146.754</v>
       </c>
       <c r="C59" s="4">
         <v>270.38</v>
@@ -3342,7 +3342,7 @@
         <v>322.97</v>
       </c>
       <c r="E59" s="4">
-        <v>0</v>
+        <v>439.7689027777778</v>
       </c>
       <c r="F59" s="4">
         <v>1660.9</v>
@@ -3354,7 +3354,7 @@
         <v>1321.25</v>
       </c>
       <c r="I59" s="4">
-        <v>0</v>
+        <v>1166.235208333334</v>
       </c>
       <c r="J59" s="4">
         <v>1873.34</v>
@@ -3363,7 +3363,7 @@
         <v>1634.36</v>
       </c>
       <c r="L59" s="4">
-        <v>0</v>
+        <v>7321.929430555552</v>
       </c>
       <c r="M59" s="4">
         <v>13055.34</v>
@@ -3377,7 +3377,7 @@
         <v>70</v>
       </c>
       <c r="B60" s="5">
-        <v>0</v>
+        <v>514.0245183887916</v>
       </c>
       <c r="C60" s="5">
         <v>125.2571110905216</v>
@@ -3386,7 +3386,7 @@
         <v>1908.806146572104</v>
       </c>
       <c r="E60" s="5">
-        <v>0</v>
+        <v>146.3846956852998</v>
       </c>
       <c r="F60" s="5">
         <v>95.7605668721136</v>
@@ -3398,7 +3398,7 @@
         <v>1759.789557805008</v>
       </c>
       <c r="I60" s="5">
-        <v>0</v>
+        <v>66.95036616263094</v>
       </c>
       <c r="J60" s="5">
         <v>115.6125799205115</v>
@@ -3407,7 +3407,7 @@
         <v>2444.085539105727</v>
       </c>
       <c r="L60" s="5">
-        <v>0</v>
+        <v>165.1374300957083</v>
       </c>
       <c r="M60" s="5">
         <v>147.1954666555423</v>
@@ -3465,7 +3465,7 @@
         <v>72</v>
       </c>
       <c r="B62" s="4">
-        <v>0</v>
+        <v>1168.3675</v>
       </c>
       <c r="C62" s="4">
         <v>913.71</v>
@@ -3474,7 +3474,7 @@
         <v>928.53</v>
       </c>
       <c r="E62" s="4">
-        <v>0</v>
+        <v>2108.6475</v>
       </c>
       <c r="F62" s="4">
         <v>6395.97</v>
@@ -3486,7 +3486,7 @@
         <v>6499.71</v>
       </c>
       <c r="I62" s="4">
-        <v>0</v>
+        <v>6162.2335</v>
       </c>
       <c r="J62" s="4">
         <v>5482.26</v>
@@ -3495,7 +3495,7 @@
         <v>5571.18</v>
       </c>
       <c r="L62" s="4">
-        <v>0</v>
+        <v>67611.98676388888</v>
       </c>
       <c r="M62" s="4">
         <v>61218.57</v>
@@ -3597,7 +3597,7 @@
         <v>75</v>
       </c>
       <c r="B65" s="4">
-        <v>150.6626666666667</v>
+        <v>1549.829111111111</v>
       </c>
       <c r="C65" s="4">
         <v>908.27</v>
@@ -3606,7 +3606,7 @@
         <v>1451.5</v>
       </c>
       <c r="E65" s="4">
-        <v>300.9363333333333</v>
+        <v>2778.437</v>
       </c>
       <c r="F65" s="4">
         <v>7757.12</v>
@@ -3618,7 +3618,7 @@
         <v>8688.129999999999</v>
       </c>
       <c r="I65" s="4">
-        <v>451.9656666666667</v>
+        <v>8862.698958333332</v>
       </c>
       <c r="J65" s="4">
         <v>6912.04</v>
@@ -3627,7 +3627,7 @@
         <v>9351.16</v>
       </c>
       <c r="L65" s="4">
-        <v>3767.816</v>
+        <v>99056.90383333337</v>
       </c>
       <c r="M65" s="4">
         <v>66507.14999999999</v>
@@ -3641,7 +3641,7 @@
         <v>76</v>
       </c>
       <c r="B66" s="5">
-        <v>1.861818888818863</v>
+        <v>19.15206452499634</v>
       </c>
       <c r="C66" s="5">
         <v>10.57849988353133</v>
@@ -3650,7 +3650,7 @@
         <v>21.9092024688041</v>
       </c>
       <c r="E66" s="5">
-        <v>1.762286545950851</v>
+        <v>16.27055825940607</v>
       </c>
       <c r="F66" s="5">
         <v>10.35815673863985</v>
@@ -3662,7 +3662,7 @@
         <v>21.81070310097466</v>
       </c>
       <c r="I66" s="5">
-        <v>0.7237411978164842</v>
+        <v>14.19200800648812</v>
       </c>
       <c r="J66" s="5">
         <v>10.47012275663164</v>
@@ -3671,7 +3671,7 @@
         <v>16.19325595591132</v>
       </c>
       <c r="L66" s="5">
-        <v>0.7094245096296652</v>
+        <v>18.65096263389599</v>
       </c>
       <c r="M66" s="5">
         <v>18.18784078024832</v>
@@ -3685,7 +3685,7 @@
         <v>77</v>
       </c>
       <c r="B67" s="4">
-        <v>16358.39</v>
+        <v>16379.89</v>
       </c>
       <c r="C67" s="4">
         <v>16399.88</v>
@@ -3694,7 +3694,7 @@
         <v>13795.09</v>
       </c>
       <c r="E67" s="4">
-        <v>38154.09</v>
+        <v>38175.59</v>
       </c>
       <c r="F67" s="4">
         <v>143043.4</v>
@@ -3706,7 +3706,7 @@
         <v>113199.95</v>
       </c>
       <c r="I67" s="4">
-        <v>144890.1</v>
+        <v>144911.6</v>
       </c>
       <c r="J67" s="4">
         <v>126096.87</v>
@@ -3715,7 +3715,7 @@
         <v>116634.43</v>
       </c>
       <c r="L67" s="4">
-        <v>877111.88</v>
+        <v>877133.38</v>
       </c>
       <c r="M67" s="4">
         <v>698452.79</v>
@@ -3729,7 +3729,7 @@
         <v>78</v>
       </c>
       <c r="B68" s="4">
-        <v>341.3746666666667</v>
+        <v>3054.703444444445</v>
       </c>
       <c r="C68" s="4">
         <v>2597.04</v>
@@ -3738,7 +3738,7 @@
         <v>2346.7</v>
       </c>
       <c r="E68" s="4">
-        <v>556.1665</v>
+        <v>6121.841361111111</v>
       </c>
       <c r="F68" s="4">
         <v>17820.02</v>
@@ -3750,7 +3750,7 @@
         <v>17146.63</v>
       </c>
       <c r="I68" s="4">
-        <v>1371.012986111111</v>
+        <v>21132.78104166667</v>
       </c>
       <c r="J68" s="4">
         <v>15402.61</v>
@@ -3759,7 +3759,7 @@
         <v>16424.63</v>
       </c>
       <c r="L68" s="4">
-        <v>14735.727875</v>
+        <v>146888.8096250004</v>
       </c>
       <c r="M68" s="4">
         <v>101302.89</v>
@@ -3773,7 +3773,7 @@
         <v>79</v>
       </c>
       <c r="B69" s="5">
-        <v>2.086847585041478</v>
+        <v>18.64910841552932</v>
       </c>
       <c r="C69" s="5">
         <v>15.83572562726069</v>
@@ -3782,7 +3782,7 @@
         <v>17.0111249727258</v>
       </c>
       <c r="E69" s="5">
-        <v>1.457685139391347</v>
+        <v>16.03600981965468</v>
       </c>
       <c r="F69" s="5">
         <v>12.45777155744341</v>
@@ -3794,7 +3794,7 @@
         <v>15.14720633710527</v>
       </c>
       <c r="I69" s="5">
-        <v>0.9462433845453283</v>
+        <v>14.58322248989499</v>
       </c>
       <c r="J69" s="5">
         <v>12.21490271725222</v>
@@ -3803,7 +3803,7 @@
         <v>14.0821453836573</v>
       </c>
       <c r="L69" s="5">
-        <v>1.680028307791248</v>
+        <v>16.74646216576553</v>
       </c>
       <c r="M69" s="5">
         <v>14.50389939740952</v>
@@ -3861,7 +3861,7 @@
         <v>81</v>
       </c>
       <c r="B71" s="4">
-        <v>0</v>
+        <v>289.8708194444445</v>
       </c>
       <c r="C71" s="4">
         <v>301.3</v>
@@ -3870,7 +3870,7 @@
         <v>279.44</v>
       </c>
       <c r="E71" s="4">
-        <v>0</v>
+        <v>576.0737222222222</v>
       </c>
       <c r="F71" s="4">
         <v>2772.82</v>
@@ -3882,7 +3882,7 @@
         <v>2599.25</v>
       </c>
       <c r="I71" s="4">
-        <v>220.51825</v>
+        <v>2064.963194444445</v>
       </c>
       <c r="J71" s="4">
         <v>2490.77</v>
@@ -3891,7 +3891,7 @@
         <v>2612.21</v>
       </c>
       <c r="L71" s="4">
-        <v>719.6010000000001</v>
+        <v>25887.51616666666</v>
       </c>
       <c r="M71" s="4">
         <v>25671.38</v>
@@ -3905,7 +3905,7 @@
         <v>82</v>
       </c>
       <c r="B72" s="5">
-        <v>0</v>
+        <v>49.75383523187801</v>
       </c>
       <c r="C72" s="5">
         <v>27.58096702733381</v>
@@ -3914,7 +3914,7 @@
         <v>46.45719035743973</v>
       </c>
       <c r="E72" s="5">
-        <v>0</v>
+        <v>57.51190246413176</v>
       </c>
       <c r="F72" s="5">
         <v>36.26051727880695</v>
@@ -3926,7 +3926,7 @@
         <v>49.87604146278749</v>
       </c>
       <c r="I72" s="5">
-        <v>4.61130732813062</v>
+        <v>43.18091546101822</v>
       </c>
       <c r="J72" s="5">
         <v>38.00079944831963</v>
@@ -3935,7 +3935,7 @@
         <v>40.41772976452221</v>
       </c>
       <c r="L72" s="5">
-        <v>1.241312891834119</v>
+        <v>44.6560073641469</v>
       </c>
       <c r="M72" s="5">
         <v>40.5632537849628</v>
@@ -3993,7 +3993,7 @@
         <v>84</v>
       </c>
       <c r="B74" s="4">
-        <v>0</v>
+        <v>718.5005555555555</v>
       </c>
       <c r="C74" s="4">
         <v>557.02</v>
@@ -4002,7 +4002,7 @@
         <v>416.46</v>
       </c>
       <c r="E74" s="4">
-        <v>0</v>
+        <v>1487.756652777778</v>
       </c>
       <c r="F74" s="4">
         <v>4768.08</v>
@@ -4014,7 +4014,7 @@
         <v>1284.62</v>
       </c>
       <c r="I74" s="4">
-        <v>0</v>
+        <v>5419.159</v>
       </c>
       <c r="J74" s="4">
         <v>4228.36</v>
@@ -4023,7 +4023,7 @@
         <v>1366.19</v>
       </c>
       <c r="L74" s="4">
-        <v>75.61266666666666</v>
+        <v>25529.7991111111</v>
       </c>
       <c r="M74" s="4">
         <v>15629.97</v>
@@ -4037,7 +4037,7 @@
         <v>85</v>
       </c>
       <c r="B75" s="5">
-        <v>0</v>
+        <v>58.10008858987559</v>
       </c>
       <c r="C75" s="5">
         <v>18.57197632741519</v>
@@ -4046,7 +4046,7 @@
         <v>23.67810602442519</v>
       </c>
       <c r="E75" s="5">
-        <v>0</v>
+        <v>48.05027542277846</v>
       </c>
       <c r="F75" s="5">
         <v>18.22651492939828</v>
@@ -4058,7 +4058,7 @@
         <v>13.33866345474934</v>
       </c>
       <c r="I75" s="5">
-        <v>0</v>
+        <v>26.64864407671476</v>
       </c>
       <c r="J75" s="5">
         <v>18.33561641756548</v>
@@ -4067,7 +4067,7 @@
         <v>11.40309510077315</v>
       </c>
       <c r="L75" s="5">
-        <v>0.08974392450746038</v>
+        <v>30.30106548441863</v>
       </c>
       <c r="M75" s="5">
         <v>21.25130305544833</v>
@@ -4155,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="4">
-        <v>0</v>
+        <v>237.4439027777778</v>
       </c>
       <c r="M77" s="4">
         <v>0</v>
@@ -4389,7 +4389,7 @@
         <v>93</v>
       </c>
       <c r="B83" s="4">
-        <v>103.178875</v>
+        <v>543.5245833333333</v>
       </c>
       <c r="C83" s="4">
         <v>644.84</v>
@@ -4398,7 +4398,7 @@
         <v>644.3200000000001</v>
       </c>
       <c r="E83" s="4">
-        <v>234.3207916666667</v>
+        <v>1127.24775</v>
       </c>
       <c r="F83" s="4">
         <v>4085.08</v>
@@ -4410,7 +4410,7 @@
         <v>4273.65</v>
       </c>
       <c r="I83" s="4">
-        <v>861.6961666666665</v>
+        <v>4036.347555555556</v>
       </c>
       <c r="J83" s="4">
         <v>3440.24</v>
@@ -4419,7 +4419,7 @@
         <v>3229.97</v>
       </c>
       <c r="L83" s="4">
-        <v>8292.820541666666</v>
+        <v>34095.84193055555</v>
       </c>
       <c r="M83" s="4">
         <v>37261.48</v>
@@ -4521,7 +4521,7 @@
         <v>96</v>
       </c>
       <c r="B86" s="4">
-        <v>0</v>
+        <v>453.9427777777778</v>
       </c>
       <c r="C86" s="4">
         <v>338.77</v>
@@ -4530,7 +4530,7 @@
         <v>396.71</v>
       </c>
       <c r="E86" s="4">
-        <v>0</v>
+        <v>963.1184166666667</v>
       </c>
       <c r="F86" s="4">
         <v>2659.14</v>
@@ -4542,7 +4542,7 @@
         <v>3600.74</v>
       </c>
       <c r="I86" s="4">
-        <v>578.256625</v>
+        <v>2997.934319444445</v>
       </c>
       <c r="J86" s="4">
         <v>2296.9</v>
@@ -4551,7 +4551,7 @@
         <v>2659.33</v>
       </c>
       <c r="L86" s="4">
-        <v>3601.116888888889</v>
+        <v>25237.12534722223</v>
       </c>
       <c r="M86" s="4">
         <v>20515.38</v>
@@ -4653,7 +4653,7 @@
         <v>99</v>
       </c>
       <c r="B89" s="4">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C89" s="4">
         <v>250.06</v>
@@ -4662,7 +4662,7 @@
         <v>208.58</v>
       </c>
       <c r="E89" s="4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F89" s="4">
         <v>1750.42</v>
@@ -4674,7 +4674,7 @@
         <v>1460.06</v>
       </c>
       <c r="I89" s="4">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J89" s="4">
         <v>1500.36</v>
@@ -4683,7 +4683,7 @@
         <v>1251.48</v>
       </c>
       <c r="L89" s="4">
-        <v>0</v>
+        <v>16750</v>
       </c>
       <c r="M89" s="4">
         <v>16754.02</v>
@@ -4917,7 +4917,7 @@
         <v>105</v>
       </c>
       <c r="B95" s="4">
-        <v>313.51575</v>
+        <v>904.1718611111111</v>
       </c>
       <c r="C95" s="4">
         <v>414.83</v>
@@ -4926,7 +4926,7 @@
         <v>988.6799999999999</v>
       </c>
       <c r="E95" s="4">
-        <v>313.51575</v>
+        <v>1746.755083333333</v>
       </c>
       <c r="F95" s="4">
         <v>4562.13</v>
@@ -4938,7 +4938,7 @@
         <v>4058.3</v>
       </c>
       <c r="I95" s="4">
-        <v>686.9094166666666</v>
+        <v>6189.003166666666</v>
       </c>
       <c r="J95" s="4">
         <v>4379.03</v>
@@ -4947,7 +4947,7 @@
         <v>4087.89</v>
       </c>
       <c r="L95" s="4">
-        <v>1522.520208333333</v>
+        <v>27821.34608333332</v>
       </c>
       <c r="M95" s="4">
         <v>26136.73</v>
@@ -5049,7 +5049,7 @@
         <v>108</v>
       </c>
       <c r="B98" s="4">
-        <v>0</v>
+        <v>178.08</v>
       </c>
       <c r="C98" s="4">
         <v>572.1</v>
@@ -5058,7 +5058,7 @@
         <v>392.09</v>
       </c>
       <c r="E98" s="4">
-        <v>0</v>
+        <v>876.6364444444444</v>
       </c>
       <c r="F98" s="4">
         <v>3391.84</v>
@@ -5070,7 +5070,7 @@
         <v>3124.43</v>
       </c>
       <c r="I98" s="4">
-        <v>0</v>
+        <v>5353.177555555554</v>
       </c>
       <c r="J98" s="4">
         <v>2907.29</v>
@@ -5079,7 +5079,7 @@
         <v>4588.59</v>
       </c>
       <c r="L98" s="4">
-        <v>0</v>
+        <v>38659.20379166667</v>
       </c>
       <c r="M98" s="4">
         <v>27627.83</v>
@@ -5181,7 +5181,7 @@
         <v>111</v>
       </c>
       <c r="B101" s="4">
-        <v>0</v>
+        <v>937.7803888888889</v>
       </c>
       <c r="C101" s="4">
         <v>637.5700000000001</v>
@@ -5190,7 +5190,7 @@
         <v>1230.32</v>
       </c>
       <c r="E101" s="4">
-        <v>428.5555833333333</v>
+        <v>2352.905055555556</v>
       </c>
       <c r="F101" s="4">
         <v>6554.31</v>
@@ -5202,7 +5202,7 @@
         <v>6116.07</v>
       </c>
       <c r="I101" s="4">
-        <v>687.831875</v>
+        <v>6326.017388888887</v>
       </c>
       <c r="J101" s="4">
         <v>5534.11</v>
@@ -5211,7 +5211,7 @@
         <v>5100.53</v>
       </c>
       <c r="L101" s="4">
-        <v>4560.945124999999</v>
+        <v>50501.83129166665</v>
       </c>
       <c r="M101" s="4">
         <v>42027.32</v>
@@ -5313,7 +5313,7 @@
         <v>114</v>
       </c>
       <c r="B104" s="4">
-        <v>0</v>
+        <v>906.4485277777777</v>
       </c>
       <c r="C104" s="4">
         <v>589.33</v>
@@ -5322,7 +5322,7 @@
         <v>1004.08</v>
       </c>
       <c r="E104" s="4">
-        <v>0</v>
+        <v>1542.214361111111</v>
       </c>
       <c r="F104" s="4">
         <v>5004.43</v>
@@ -5334,7 +5334,7 @@
         <v>5643.7</v>
       </c>
       <c r="I104" s="4">
-        <v>28.01244444444444</v>
+        <v>4802.405777777778</v>
       </c>
       <c r="J104" s="4">
         <v>4415.1</v>
@@ -5343,7 +5343,7 @@
         <v>4620.76</v>
       </c>
       <c r="L104" s="4">
-        <v>314.5710694444444</v>
+        <v>52453.42520833333</v>
       </c>
       <c r="M104" s="4">
         <v>47657.25</v>
@@ -5454,7 +5454,7 @@
         <v>644.39</v>
       </c>
       <c r="E107" s="4">
-        <v>0</v>
+        <v>321.0228333333333</v>
       </c>
       <c r="F107" s="4">
         <v>2491.85</v>
@@ -5466,7 +5466,7 @@
         <v>2910.9</v>
       </c>
       <c r="I107" s="4">
-        <v>0</v>
+        <v>2225.88395</v>
       </c>
       <c r="J107" s="4">
         <v>1931.78</v>
@@ -5475,7 +5475,7 @@
         <v>1791.25</v>
       </c>
       <c r="L107" s="4">
-        <v>0</v>
+        <v>23765.05497222223</v>
       </c>
       <c r="M107" s="4">
         <v>20329.09</v>
@@ -5607,7 +5607,7 @@
         <v>180.1</v>
       </c>
       <c r="L110" s="4">
-        <v>1422.012888888889</v>
+        <v>3071.948249999999</v>
       </c>
       <c r="M110" s="4">
         <v>0</v>
@@ -5709,7 +5709,7 @@
         <v>123</v>
       </c>
       <c r="B113" s="4">
-        <v>0</v>
+        <v>616.0930833333334</v>
       </c>
       <c r="C113" s="4">
         <v>581.37</v>
@@ -5718,7 +5718,7 @@
         <v>567.91</v>
       </c>
       <c r="E113" s="4">
-        <v>0</v>
+        <v>1952.267347222222</v>
       </c>
       <c r="F113" s="4">
         <v>4179.93</v>
@@ -5730,7 +5730,7 @@
         <v>3757.2</v>
       </c>
       <c r="I113" s="4">
-        <v>0</v>
+        <v>6848.069791666668</v>
       </c>
       <c r="J113" s="4">
         <v>3598.56</v>
@@ -5739,7 +5739,7 @@
         <v>3507.32</v>
       </c>
       <c r="L113" s="4">
-        <v>0</v>
+        <v>48805.84104999997</v>
       </c>
       <c r="M113" s="4">
         <v>26327.16</v>
@@ -5973,7 +5973,7 @@
         <v>129</v>
       </c>
       <c r="B119" s="4">
-        <v>0</v>
+        <v>650.2994444444444</v>
       </c>
       <c r="C119" s="4">
         <v>587.05</v>
@@ -5982,7 +5982,7 @@
         <v>1067.38</v>
       </c>
       <c r="E119" s="4">
-        <v>0</v>
+        <v>1169.818333333333</v>
       </c>
       <c r="F119" s="4">
         <v>3557.35</v>
@@ -5994,7 +5994,7 @@
         <v>3239.84</v>
       </c>
       <c r="I119" s="4">
-        <v>0</v>
+        <v>3094.445555555556</v>
       </c>
       <c r="J119" s="4">
         <v>3246.3</v>
@@ -6003,7 +6003,7 @@
         <v>2336.61</v>
       </c>
       <c r="L119" s="4">
-        <v>0</v>
+        <v>38967.26540277778</v>
       </c>
       <c r="M119" s="4">
         <v>35756.35</v>
@@ -6135,7 +6135,7 @@
         <v>5586.24</v>
       </c>
       <c r="L122" s="4">
-        <v>0</v>
+        <v>17360</v>
       </c>
       <c r="M122" s="4">
         <v>39806.58</v>
@@ -6179,7 +6179,7 @@
         <v>6206.933333333333</v>
       </c>
       <c r="L123" s="5">
-        <v>0</v>
+        <v>3773913.043478261</v>
       </c>
       <c r="M123" s="5">
         <v>40.09042017483785</v>
@@ -6237,7 +6237,7 @@
         <v>135</v>
       </c>
       <c r="B125" s="4">
-        <v>0</v>
+        <v>1167.588277777778</v>
       </c>
       <c r="C125" s="4">
         <v>980.3099999999999</v>
@@ -6246,7 +6246,7 @@
         <v>898.23</v>
       </c>
       <c r="E125" s="4">
-        <v>0</v>
+        <v>2190.033555555556</v>
       </c>
       <c r="F125" s="4">
         <v>6115.47</v>
@@ -6258,7 +6258,7 @@
         <v>5635.32</v>
       </c>
       <c r="I125" s="4">
-        <v>0</v>
+        <v>5929.415</v>
       </c>
       <c r="J125" s="4">
         <v>5201.46</v>
@@ -6267,7 +6267,7 @@
         <v>4406.16</v>
       </c>
       <c r="L125" s="4">
-        <v>0</v>
+        <v>59426.59123611111</v>
       </c>
       <c r="M125" s="4">
         <v>58134.47</v>
@@ -6369,7 +6369,7 @@
         <v>138</v>
       </c>
       <c r="B128" s="4">
-        <v>0</v>
+        <v>821.92</v>
       </c>
       <c r="C128" s="4">
         <v>846.78</v>
@@ -6378,7 +6378,7 @@
         <v>824.1799999999999</v>
       </c>
       <c r="E128" s="4">
-        <v>0</v>
+        <v>1643.84</v>
       </c>
       <c r="F128" s="4">
         <v>5927.46</v>
@@ -6390,7 +6390,7 @@
         <v>5769.26</v>
       </c>
       <c r="I128" s="4">
-        <v>0</v>
+        <v>4931.52</v>
       </c>
       <c r="J128" s="4">
         <v>5080.68</v>
@@ -6399,7 +6399,7 @@
         <v>4945.08</v>
       </c>
       <c r="L128" s="4">
-        <v>0</v>
+        <v>55068.64</v>
       </c>
       <c r="M128" s="4">
         <v>56734.26</v>
@@ -6501,7 +6501,7 @@
         <v>141</v>
       </c>
       <c r="B131" s="4">
-        <v>0</v>
+        <v>567.9918888888889</v>
       </c>
       <c r="C131" s="4">
         <v>410.8</v>
@@ -6510,7 +6510,7 @@
         <v>381.12</v>
       </c>
       <c r="E131" s="4">
-        <v>0</v>
+        <v>1141.684944444444</v>
       </c>
       <c r="F131" s="4">
         <v>3230.75</v>
@@ -6522,7 +6522,7 @@
         <v>3306.23</v>
       </c>
       <c r="I131" s="4">
-        <v>0</v>
+        <v>2583.439944444444</v>
       </c>
       <c r="J131" s="4">
         <v>2885.24</v>
@@ -6531,7 +6531,7 @@
         <v>2932.16</v>
       </c>
       <c r="L131" s="4">
-        <v>0</v>
+        <v>30707.50744444445</v>
       </c>
       <c r="M131" s="4">
         <v>31043.77</v>
@@ -6633,7 +6633,7 @@
         <v>144</v>
       </c>
       <c r="B134" s="4">
-        <v>0</v>
+        <v>216.44</v>
       </c>
       <c r="C134" s="4">
         <v>144.38</v>
@@ -6642,7 +6642,7 @@
         <v>208.58</v>
       </c>
       <c r="E134" s="4">
-        <v>0</v>
+        <v>432.88</v>
       </c>
       <c r="F134" s="4">
         <v>1010.66</v>
@@ -6654,7 +6654,7 @@
         <v>2104.64</v>
       </c>
       <c r="I134" s="4">
-        <v>0</v>
+        <v>1298.64</v>
       </c>
       <c r="J134" s="4">
         <v>866.28</v>
@@ -6663,7 +6663,7 @@
         <v>1738.82</v>
       </c>
       <c r="L134" s="4">
-        <v>0</v>
+        <v>14817.26280555555</v>
       </c>
       <c r="M134" s="4">
         <v>9673.459999999999</v>
@@ -6765,7 +6765,7 @@
         <v>147</v>
       </c>
       <c r="B137" s="4">
-        <v>0</v>
+        <v>623.97</v>
       </c>
       <c r="C137" s="4">
         <v>624.21</v>
@@ -6774,7 +6774,7 @@
         <v>777.4</v>
       </c>
       <c r="E137" s="4">
-        <v>0</v>
+        <v>1247.94</v>
       </c>
       <c r="F137" s="4">
         <v>4891.47</v>
@@ -6786,7 +6786,7 @@
         <v>4963.68</v>
       </c>
       <c r="I137" s="4">
-        <v>0</v>
+        <v>3743.82</v>
       </c>
       <c r="J137" s="4">
         <v>4267.26</v>
@@ -6795,7 +6795,7 @@
         <v>3507.89</v>
       </c>
       <c r="L137" s="4">
-        <v>0</v>
+        <v>41805.99</v>
       </c>
       <c r="M137" s="4">
         <v>45476.07</v>
@@ -7191,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="4">
-        <v>0</v>
+        <v>487.4147916666667</v>
       </c>
       <c r="M146" s="4">
         <v>0</v>
@@ -7323,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="4">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="M149" s="4">
         <v>0</v>
@@ -7455,7 +7455,7 @@
         <v>403.62</v>
       </c>
       <c r="L152" s="4">
-        <v>0</v>
+        <v>554.7129833333333</v>
       </c>
       <c r="M152" s="4">
         <v>0</v>
@@ -7587,7 +7587,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="4">
-        <v>0</v>
+        <v>2898.262472222222</v>
       </c>
       <c r="M155" s="4">
         <v>0</v>
@@ -7719,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="4">
-        <v>0</v>
+        <v>106.4046527777778</v>
       </c>
       <c r="M158" s="4">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="4">
-        <v>0</v>
+        <v>216.6333333333334</v>
       </c>
       <c r="M161" s="4">
         <v>0</v>
@@ -8115,7 +8115,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="4">
-        <v>0</v>
+        <v>1207.070888888889</v>
       </c>
       <c r="M167" s="4">
         <v>0</v>
@@ -8247,7 +8247,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="4">
-        <v>0</v>
+        <v>24.909</v>
       </c>
       <c r="M170" s="4">
         <v>0</v>
@@ -8305,7 +8305,7 @@
         <v>182</v>
       </c>
       <c r="B174" s="4">
-        <v>174239.62</v>
+        <v>174261.12</v>
       </c>
       <c r="C174" s="4">
         <v>188509.38</v>
@@ -8314,7 +8314,7 @@
         <v>192944.07</v>
       </c>
       <c r="E174" s="4">
-        <v>400781.4099999999</v>
+        <v>400802.9099999999</v>
       </c>
       <c r="F174" s="4">
         <v>2033575.15</v>
@@ -8326,7 +8326,7 @@
         <v>757383.74</v>
       </c>
       <c r="I174" s="4">
-        <v>1786814.3</v>
+        <v>1786835.8</v>
       </c>
       <c r="J174" s="4">
         <v>1880221.85</v>
@@ -8335,7 +8335,7 @@
         <v>1109222.21</v>
       </c>
       <c r="L174" s="4">
-        <v>9514607.000000004</v>
+        <v>9514628.500000004</v>
       </c>
       <c r="M174" s="4">
         <v>10054869.34</v>
@@ -8349,7 +8349,7 @@
         <v>183</v>
       </c>
       <c r="B175" s="4">
-        <v>1161.559333333333</v>
+        <v>39051.24806944445</v>
       </c>
       <c r="C175" s="4">
         <v>40116.54</v>
@@ -8358,7 +8358,7 @@
         <v>41349.05000000002</v>
       </c>
       <c r="E175" s="4">
-        <v>2802.180194444445</v>
+        <v>78811.88373611109</v>
       </c>
       <c r="F175" s="4">
         <v>310103.1299999999</v>
@@ -8370,7 +8370,7 @@
         <v>284515.6</v>
       </c>
       <c r="I175" s="4">
-        <v>9534.112038888888</v>
+        <v>250000.4855722222</v>
       </c>
       <c r="J175" s="4">
         <v>258478.2399999999</v>
@@ -8379,7 +8379,7 @@
         <v>327903.58</v>
       </c>
       <c r="L175" s="4">
-        <v>82951.13657777777</v>
+        <v>2388597.749888889</v>
       </c>
       <c r="M175" s="4">
         <v>2136607.77</v>
@@ -8393,7 +8393,7 @@
         <v>184</v>
       </c>
       <c r="B176" s="5">
-        <v>0.6666447810970509</v>
+        <v>22.40961613780771</v>
       </c>
       <c r="C176" s="5">
         <v>21.28092511895164</v>
@@ -8402,7 +8402,7 @@
         <v>21.43058866748276</v>
       </c>
       <c r="E176" s="5">
-        <v>0.6991791845945264</v>
+        <v>19.66350088029828</v>
       </c>
       <c r="F176" s="5">
         <v>15.24916008144572</v>
@@ -8414,7 +8414,7 @@
         <v>37.56558069229212</v>
       </c>
       <c r="I176" s="5">
-        <v>0.5335815836535944</v>
+        <v>13.99124002173128</v>
       </c>
       <c r="J176" s="5">
         <v>13.74722030807162</v>
@@ -8423,7 +8423,7 @@
         <v>29.56157720642828</v>
       </c>
       <c r="L176" s="5">
-        <v>0.8718293522557236</v>
+        <v>25.10447727821311</v>
       </c>
       <c r="M176" s="5">
         <v>21.24948318821217</v>
@@ -8437,7 +8437,7 @@
         <v>185</v>
       </c>
       <c r="B177" s="4">
-        <v>173078.0606666666</v>
+        <v>135209.8719305555</v>
       </c>
       <c r="C177" s="4">
         <v>148392.84</v>
@@ -8446,7 +8446,7 @@
         <v>151595.02</v>
       </c>
       <c r="E177" s="4">
-        <v>397979.2298055554</v>
+        <v>321991.0262638888</v>
       </c>
       <c r="F177" s="4">
         <v>1723472.02</v>
@@ -8458,7 +8458,7 @@
         <v>472868.14</v>
       </c>
       <c r="I177" s="4">
-        <v>1777280.187961111</v>
+        <v>1536835.314427778</v>
       </c>
       <c r="J177" s="4">
         <v>1621743.61</v>
@@ -8467,7 +8467,7 @@
         <v>781318.63</v>
       </c>
       <c r="L177" s="4">
-        <v>9431655.863422226</v>
+        <v>7126030.750111114</v>
       </c>
       <c r="M177" s="4">
         <v>7918261.569999998</v>
